--- a/results/main/Table_1.xlsx
+++ b/results/main/Table_1.xlsx
@@ -490,10 +490,10 @@
         <v>708</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>63823</v>
+        <v>64810</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>5</v>
@@ -505,10 +505,10 @@
         <v>25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="4">
@@ -532,10 +532,10 @@
         <v>542</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>38717</v>
+        <v>39341</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>5</v>
@@ -544,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>44</v>
@@ -561,10 +561,10 @@
         <v>166</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>25106</v>
+        <v>25469</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5</v>
@@ -573,13 +573,13 @@
         <v>42</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="7">
@@ -600,13 +600,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46426</v>
+        <v>47602</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>5</v>
@@ -615,13 +615,13 @@
         <v>16</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="9">
@@ -629,10 +629,10 @@
         <v>17</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17397</v>
+        <v>17208</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>48</v>
@@ -647,10 +647,10 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>646</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10">
@@ -674,10 +674,10 @@
         <v>367</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>18460</v>
+        <v>18631</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>7</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1488</v>
@@ -703,10 +703,10 @@
         <v>341</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45363</v>
+        <v>46179</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
@@ -715,13 +715,13 @@
         <v>18</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="13">
@@ -745,10 +745,10 @@
         <v>43</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2418</v>
+        <v>2449</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>6</v>
@@ -760,10 +760,10 @@
         <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>646</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15">
@@ -774,10 +774,10 @@
         <v>665</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>61405</v>
+        <v>62361</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>5</v>
@@ -789,10 +789,10 @@
         <v>25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
   </sheetData>

--- a/results/main/Table_1.xlsx
+++ b/results/main/Table_1.xlsx
@@ -600,13 +600,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>47602</v>
+        <v>46426</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>5</v>
@@ -615,13 +615,13 @@
         <v>16</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1522</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
@@ -629,10 +629,10 @@
         <v>17</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17208</v>
+        <v>17397</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>48</v>
@@ -647,10 +647,10 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>661</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10">
